--- a/Tagihan/Izal/Al.Co.xlsx
+++ b/Tagihan/Izal/Al.Co.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\Izal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84427B20-14DD-4102-A1CC-65E9B80088E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{352A1DB1-6462-4FE5-90E4-C209BE7DF439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>NO.</t>
   </si>
@@ -81,13 +81,19 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>Mtr</t>
+  </si>
+  <si>
     <t>Lot</t>
   </si>
   <si>
-    <t xml:space="preserve">Pasang Ezviz </t>
-  </si>
-  <si>
-    <t>Kepada Tuan/Nyonya  AL.CO</t>
+    <t>Pasang Ezviz</t>
+  </si>
+  <si>
+    <t>Kabel Listrik</t>
+  </si>
+  <si>
+    <t>Kepada Tuan/Nyonya     AL.CO</t>
   </si>
   <si>
     <r>
@@ -218,7 +224,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -449,21 +455,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -510,6 +501,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -601,9 +595,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -677,13 +668,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>154781</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>23812</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2320131</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>79851</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1018,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B5:N39"/>
+  <dimension ref="B5:N38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" customWidth="1"/>
@@ -1026,81 +1017,81 @@
     <col min="3" max="3" width="43.7109375" customWidth="1"/>
     <col min="4" max="4" width="6.140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" style="16" customWidth="1"/>
     <col min="8" max="8" width="2.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:14" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
     </row>
     <row r="10" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
     </row>
     <row r="12" spans="2:14" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
     </row>
     <row r="13" spans="2:14" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="48"/>
+      <c r="F13" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="49"/>
       <c r="N13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="2:14" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="49"/>
+      <c r="F14" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="50"/>
     </row>
     <row r="15" spans="2:14" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C15" s="9"/>
@@ -1116,13 +1107,13 @@
       <c r="D16" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="51" t="s">
+      <c r="E16" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="19" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1130,194 +1121,199 @@
       <c r="B17" s="8">
         <v>1</v>
       </c>
-      <c r="C17" s="31" t="s">
-        <v>17</v>
+      <c r="C17" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="E17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="27">
         <v>75000</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <f>D17*F17</f>
         <v>75000</v>
       </c>
     </row>
     <row r="18" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="27"/>
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="29">
+        <v>5000</v>
+      </c>
+      <c r="G18" s="28">
+        <f t="shared" ref="G18:G21" si="0">D18*F18</f>
+        <v>10000</v>
+      </c>
     </row>
     <row r="19" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
-      <c r="C19" s="32"/>
+      <c r="C19" s="33"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="27"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="28"/>
     </row>
     <row r="20" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
-      <c r="C20" s="32"/>
+      <c r="C20" s="33"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="27"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
-      <c r="C21" s="32"/>
+      <c r="C21" s="33"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="27"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="28"/>
     </row>
     <row r="22" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="27"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="28"/>
     </row>
     <row r="23" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
-      <c r="C23" s="33"/>
+      <c r="C23" s="34"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="27"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="28"/>
     </row>
     <row r="24" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
-      <c r="C24" s="33"/>
+      <c r="C24" s="34"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="27"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="28"/>
     </row>
     <row r="25" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="12"/>
-      <c r="C25" s="33"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="34"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="27"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="28"/>
     </row>
     <row r="26" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="33"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="34"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="27"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="28"/>
     </row>
     <row r="27" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
-      <c r="C27" s="33"/>
+      <c r="C27" s="34"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="27"/>
-    </row>
-    <row r="28" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="30"/>
+      <c r="G27" s="28"/>
+    </row>
+    <row r="28" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="5"/>
-      <c r="C28" s="33"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="27"/>
-    </row>
-    <row r="29" spans="2:7" s="6" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="2:7" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="43" t="s">
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+    </row>
+    <row r="29" spans="2:7" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="30">
-        <f>SUM(G17:G29)</f>
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="33" spans="2:8" s="22" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B33" s="46" t="s">
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="31">
+        <f>SUM(G17:G28)</f>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="32" spans="2:7" s="23" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B32" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="46"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="47" t="s">
+      <c r="C32" s="47"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="47"/>
-    </row>
-    <row r="37" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
+      <c r="G32" s="48"/>
+    </row>
+    <row r="36" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="24"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="38" t="s">
+      <c r="B38" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="24"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="C7:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="B14:C14"/>
